--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>108802</v>
+        <v>109057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,6 +1018,16 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Vägslänt i lövskog</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>1148</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109057</v>
+        <v>109063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109063</v>
+        <v>109065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109065</v>
+        <v>109066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109066</v>
+        <v>109072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109072</v>
+        <v>109076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109076</v>
+        <v>109078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109078</v>
+        <v>109080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109080</v>
+        <v>109093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109093</v>
+        <v>109095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109095</v>
+        <v>109100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109100</v>
+        <v>109121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109121</v>
+        <v>109122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109122</v>
+        <v>109127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109127</v>
+        <v>109130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109130</v>
+        <v>109136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109136</v>
+        <v>109137</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109137</v>
+        <v>109149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109149</v>
+        <v>109150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109150</v>
+        <v>109153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109153</v>
+        <v>109155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2025 artfynd.xlsx
+++ b/artfynd/A 18510-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>95309003</v>
       </c>
       <c r="B4" t="n">
-        <v>109155</v>
+        <v>109159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
